--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487716_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487716_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. GARCIA-LARRACHE SEGURA</t>
+          <t>J. MARTINEZ SANTOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1802</v>
+        <v>0.6093</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2772</v>
+        <v>1.715</v>
       </c>
       <c r="F2" t="n">
-        <v>0.903</v>
+        <v>-1.1057</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4535</v>
+        <v>-0.2901</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7993</v>
+        <v>1.8092</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.3458</v>
+        <v>-2.0994</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4614</v>
+        <v>1.8755</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4335</v>
+        <v>3.0071</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0279</v>
+        <v>-1.1317</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0079</v>
+        <v>-2.1656</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3658</v>
+        <v>-1.1979</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.3737</v>
+        <v>-0.9677</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6983</v>
+        <v>-0.5184</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6397</v>
+        <v>-0.4142</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0586</v>
+        <v>-0.1043</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.5537</v>
+        <v>1.2239</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.6597</v>
+        <v>1.2239</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ALONSO GONZÁLEZ</t>
+          <t>J. GARCIA-LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.2064</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3636</v>
+        <v>-0.1242</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1441</v>
+        <v>0.3306</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3383</v>
+        <v>0.4535</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.393</v>
+        <v>1.7993</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7313</v>
+        <v>-1.3458</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8565</v>
+        <v>1.4614</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5643</v>
+        <v>1.4335</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4209</v>
+        <v>0.0279</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5183</v>
+        <v>-1.0079</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1714</v>
+        <v>0.3658</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6896</v>
+        <v>-1.3737</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5821</v>
+        <v>0.5821</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3881</v>
+        <v>1.7463</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7245</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1951</v>
+        <v>0.2383</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5563</v>
+        <v>0.4862</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-1.5537</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2821</v>
+        <v>-0.6597</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2821</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANTOS</t>
+          <t>M. ALONSO GONZÁLEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1455</v>
+        <v>0.0349</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4147</v>
+        <v>0.1634</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2692</v>
+        <v>-0.1285</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2901</v>
+        <v>0.3383</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8092</v>
+        <v>-0.393</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.0994</v>
+        <v>0.7313</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8755</v>
+        <v>0.8565</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0071</v>
+        <v>-0.5643</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1317</v>
+        <v>1.4209</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1656</v>
+        <v>-0.5183</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1979</v>
+        <v>0.1714</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9677</v>
+        <v>-0.6896</v>
       </c>
       <c r="P4" t="n">
-        <v>0.194</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1642</v>
+        <v>0.3881</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9823</v>
+        <v>0.2787</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7145</v>
+        <v>-0.0051</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2678</v>
+        <v>0.2838</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2239</v>
+        <v>0.2821</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4999</v>
+        <v>-0.4548</v>
       </c>
       <c r="E5" t="n">
-        <v>0.098</v>
+        <v>-0.1022</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5979</v>
+        <v>-0.3526</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0844</v>
@@ -844,13 +844,13 @@
         <v>2.3284</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1752</v>
+        <v>-0.1301</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0751</v>
+        <v>-0.1251</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2503</v>
+        <v>-0.005</v>
       </c>
       <c r="V5" t="n">
         <v>1.506</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. MARTINEZ ALVAREZ</t>
+          <t>M. KREISLER LORENTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5565</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1906</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3659</v>
+        <v>-1.4567</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2861</v>
+        <v>0.4469</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0948</v>
+        <v>0.5981</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1913</v>
+        <v>-0.1512</v>
       </c>
       <c r="J6" t="n">
-        <v>0.143</v>
+        <v>1.9942</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0618</v>
+        <v>0.0989</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08119999999999999</v>
+        <v>1.8953</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.429</v>
+        <v>-1.5473</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1565</v>
+        <v>0.4992</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2725</v>
+        <v>-2.0466</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7761</v>
+        <v>0.3881</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>0.194</v>
+        <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2122</v>
+        <v>-0.3182</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3634</v>
+        <v>-0.2745</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1512</v>
+        <v>-0.0437</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. KREISLER LORENTE</t>
+          <t>E. MARTINEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5892</v>
+        <v>-1.4836</v>
       </c>
       <c r="E7" t="n">
-        <v>0.249</v>
+        <v>-1.0905</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8382</v>
+        <v>-0.3932</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4469</v>
+        <v>-0.2861</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5981</v>
+        <v>-0.0948</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1512</v>
+        <v>-0.1913</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9942</v>
+        <v>0.143</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0989</v>
+        <v>0.0618</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8953</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5473</v>
+        <v>-0.429</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4992</v>
+        <v>-0.1565</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.0466</v>
+        <v>-0.2725</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3881</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2003</v>
+        <v>-0.1394</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.775</v>
+        <v>-0.2633</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4253</v>
+        <v>0.1239</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2207</v>
+        <v>-2.1657</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2132</v>
+        <v>2.9139</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.434</v>
+        <v>-5.0797</v>
       </c>
       <c r="G8" t="n">
         <v>0.0044</v>
@@ -1078,13 +1078,13 @@
         <v>1.9403</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5819</v>
+        <v>-0.5269</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9444</v>
+        <v>-0.2437</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6375</v>
+        <v>-0.2832</v>
       </c>
       <c r="V8" t="n">
         <v>-3.3895</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LAPASTORA ARACIL</t>
+          <t>P. FUENTE DIEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6094</v>
+        <v>-3.7918</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1154</v>
+        <v>-1.6303</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.7248</v>
+        <v>-2.1616</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8767</v>
+        <v>-0.8643</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5792</v>
+        <v>-0.9054</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4559</v>
+        <v>0.0411</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3268</v>
+        <v>0.4548</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2811</v>
+        <v>-0.276</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0456</v>
+        <v>0.7307</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2035</v>
+        <v>-1.3191</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7019</v>
+        <v>-0.6294</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.5015</v>
+        <v>-0.6896</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7761</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q9" t="n">
         <v>-2.1344</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4435</v>
+        <v>-0.1514</v>
       </c>
       <c r="T9" t="n">
-        <v>0.923</v>
+        <v>0.0493</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4796</v>
+        <v>-0.2007</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4</v>
+        <v>-1.2239</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6373</v>
+        <v>-3.8638</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6522</v>
+        <v>-1.2518</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9851</v>
+        <v>-2.612</v>
       </c>
       <c r="G10" t="n">
         <v>-1.479</v>
@@ -1234,13 +1234,13 @@
         <v>1.5523</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0655</v>
+        <v>-0.1609</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8233</v>
+        <v>-0.4229</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8888</v>
+        <v>0.2619</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8358</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. FUENTE DIEZ</t>
+          <t>J. LAPASTORA ARACIL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3558</v>
+        <v>-4.0192</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0307</v>
+        <v>-0.4852</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3251</v>
+        <v>-3.534</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8643</v>
+        <v>-0.8767</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9054</v>
+        <v>0.5792</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0411</v>
+        <v>-1.4559</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4548</v>
+        <v>1.3268</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.276</v>
+        <v>1.2811</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7307</v>
+        <v>0.0456</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3191</v>
+        <v>-2.2035</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6294</v>
+        <v>-0.7019</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6896</v>
+        <v>-1.5015</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5523</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q11" t="n">
         <v>-2.1344</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5821</v>
+        <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7153</v>
+        <v>0.0336</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3511</v>
+        <v>0.3224</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3643</v>
+        <v>-0.2888</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2239</v>
+        <v>-2.4</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2239</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="12">
@@ -1348,10 +1348,10 @@
         <v>-15.6355</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8576000000000001</v>
+        <v>0.8575999999999997</v>
       </c>
       <c r="F12" t="n">
-        <v>-16.4931</v>
+        <v>-16.4934</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6375</v>
@@ -1369,13 +1369,13 @@
         <v>8.5848</v>
       </c>
       <c r="L12" t="n">
-        <v>7.6192</v>
+        <v>7.619200000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-18.8416</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.465299999999999</v>
+        <v>-4.4653</v>
       </c>
       <c r="O12" t="n">
         <v>-14.3761</v>
@@ -1390,13 +1390,13 @@
         <v>12.6121</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9084</v>
+        <v>-0.9085</v>
       </c>
       <c r="T12" t="n">
         <v>-1.1388</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2301</v>
+        <v>0.2301000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-9.179</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. MUNRO</t>
+          <t>S. MOYER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1296</v>
+        <v>5.8884</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8228</v>
+        <v>5.9034</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3068</v>
+        <v>-0.015</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4236</v>
+        <v>1.9194</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2175</v>
+        <v>-1.7449</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6411</v>
+        <v>3.6643</v>
       </c>
       <c r="J13" t="n">
-        <v>4.0908</v>
+        <v>5.0821</v>
       </c>
       <c r="K13" t="n">
-        <v>1.3429</v>
+        <v>0.033</v>
       </c>
       <c r="L13" t="n">
-        <v>2.7478</v>
+        <v>5.0491</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.6672</v>
+        <v>-3.1627</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5604</v>
+        <v>-1.7779</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1067</v>
+        <v>-1.3848</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1344</v>
+        <v>2.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3762</v>
+        <v>-0.0608</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1962</v>
+        <v>-0.2981</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1799</v>
+        <v>0.2373</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1657</v>
+        <v>3.0597</v>
       </c>
       <c r="W13" t="n">
-        <v>1.506</v>
+        <v>3.0597</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. MOYER</t>
+          <t>J. MUNRO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5843</v>
+        <v>5.1174</v>
       </c>
       <c r="E14" t="n">
-        <v>5.0025</v>
+        <v>4.6226</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4182</v>
+        <v>0.4948</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9194</v>
+        <v>1.4236</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.7449</v>
+        <v>-0.2175</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6643</v>
+        <v>1.6411</v>
       </c>
       <c r="J14" t="n">
-        <v>5.0821</v>
+        <v>4.0908</v>
       </c>
       <c r="K14" t="n">
-        <v>0.033</v>
+        <v>1.3429</v>
       </c>
       <c r="L14" t="n">
-        <v>5.0491</v>
+        <v>2.7478</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.1627</v>
+        <v>-2.6672</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7779</v>
+        <v>-1.5604</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3848</v>
+        <v>-1.1067</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9105</v>
+        <v>2.1344</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3649</v>
+        <v>0.3639</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.199</v>
+        <v>-0.004</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.166</v>
+        <v>0.3679</v>
       </c>
       <c r="V14" t="n">
-        <v>3.0597</v>
+        <v>2.1657</v>
       </c>
       <c r="W14" t="n">
-        <v>3.0597</v>
+        <v>1.506</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4301</v>
+        <v>3.5269</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0147</v>
+        <v>2.4141</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4154</v>
+        <v>1.1128</v>
       </c>
       <c r="G15" t="n">
         <v>0.0646</v>
@@ -1624,13 +1624,13 @@
         <v>2.5224</v>
       </c>
       <c r="S15" t="n">
-        <v>1.976</v>
+        <v>1.0728</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0453</v>
+        <v>0.4447</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9307</v>
+        <v>0.6281</v>
       </c>
       <c r="V15" t="n">
         <v>2.7776</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9121</v>
+        <v>3.4812</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2447</v>
+        <v>2.544</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6674</v>
+        <v>0.9371</v>
       </c>
       <c r="G16" t="n">
         <v>2.1316</v>
@@ -1702,13 +1702,13 @@
         <v>0.5821</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9163</v>
+        <v>0.4854</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0924</v>
+        <v>0.3917</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1761</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0.2821</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. ECHEVERRIA MATEO</t>
+          <t>G. HIERRO ABAD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0721</v>
+        <v>1.2163</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8128</v>
+        <v>1.5046</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7406</v>
+        <v>-0.2882</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6653</v>
+        <v>0.2287</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.0788</v>
+        <v>1.2548</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4135</v>
+        <v>-1.0261</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8692</v>
+        <v>1.237</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.1905</v>
+        <v>1.7013</v>
       </c>
       <c r="L17" t="n">
-        <v>4.0597</v>
+        <v>-0.4643</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.5345</v>
+        <v>-1.0083</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8883</v>
+        <v>-0.4466</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.6462</v>
+        <v>-0.5617</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.3881</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9403</v>
+        <v>1.3582</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2315</v>
+        <v>0.2697</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3779</v>
+        <v>0.0617</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1465</v>
+        <v>0.2081</v>
       </c>
       <c r="V17" t="n">
-        <v>1.506</v>
+        <v>0.3299</v>
       </c>
       <c r="W17" t="n">
-        <v>1.506</v>
+        <v>1.1761</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. HIERRO ABAD</t>
+          <t>E. ECHEVERRIA MATEO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8677</v>
+        <v>1.1323</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5046</v>
+        <v>2.4124</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6369</v>
+        <v>-1.2801</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2287</v>
+        <v>-0.6653</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2548</v>
+        <v>-3.0788</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0261</v>
+        <v>2.4135</v>
       </c>
       <c r="J18" t="n">
-        <v>1.237</v>
+        <v>2.8692</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7013</v>
+        <v>-1.1905</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4643</v>
+        <v>4.0597</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0083</v>
+        <v>-3.5345</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4466</v>
+        <v>-1.8883</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5617</v>
+        <v>-1.6462</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3881</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3582</v>
+        <v>1.9403</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.079</v>
+        <v>0.2916</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0617</v>
+        <v>-0.0225</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1406</v>
+        <v>0.3141</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3299</v>
+        <v>1.506</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1761</v>
+        <v>1.506</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8462</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2273</v>
+        <v>0.428</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3875</v>
+        <v>-0.887</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6148</v>
+        <v>1.315</v>
       </c>
       <c r="G19" t="n">
         <v>-0.275</v>
@@ -1936,13 +1936,13 @@
         <v>1.1642</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3082</v>
+        <v>0.5089</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6057</v>
+        <v>-0.1052</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9139</v>
+        <v>0.6141</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. PRATS PEINADO</t>
+          <t>J. BARRA DE LA CRUZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9006</v>
+        <v>-1.8563</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6169</v>
+        <v>-0.5041</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2838</v>
+        <v>-1.3522</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2885</v>
+        <v>0.0983</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8848</v>
+        <v>0.7884</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4036</v>
+        <v>-0.6901</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2535</v>
+        <v>2.5595</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6673</v>
+        <v>2.4098</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5861</v>
+        <v>0.1496</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.035</v>
+        <v>-2.4612</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2175</v>
+        <v>-1.6214</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8175</v>
+        <v>-0.8398</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3881</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3881</v>
+        <v>2.5224</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0002</v>
+        <v>-0.6247</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3634</v>
+        <v>-0.4352</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3632</v>
+        <v>-0.1895</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.9418</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BARRA DE LA CRUZ</t>
+          <t>J. PRATS PEINADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6871</v>
+        <v>-1.9641</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9045</v>
+        <v>-1.5168</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7826</v>
+        <v>-0.4473</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0983</v>
+        <v>-2.2885</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7884</v>
+        <v>-0.8848</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6901</v>
+        <v>-1.4036</v>
       </c>
       <c r="J21" t="n">
-        <v>2.5595</v>
+        <v>-1.2535</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4098</v>
+        <v>-0.6673</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1496</v>
+        <v>-0.5861</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4612</v>
+        <v>-1.035</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6214</v>
+        <v>-0.2175</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8398</v>
+        <v>-0.8175</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3881</v>
+        <v>0.3881</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5224</v>
+        <v>0.3881</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4556</v>
+        <v>-0.0636</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8356</v>
+        <v>-0.2633</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.62</v>
+        <v>0.1996</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9418</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>15.6355</v>
+        <v>16.9701</v>
       </c>
       <c r="E22" t="n">
         <v>16.4932</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8577000000000001</v>
+        <v>0.4768999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>2.6374</v>
@@ -2140,13 +2140,13 @@
         <v>-4.1193</v>
       </c>
       <c r="I22" t="n">
-        <v>6.756799999999998</v>
+        <v>6.756799999999999</v>
       </c>
       <c r="J22" t="n">
         <v>18.8416</v>
       </c>
       <c r="K22" t="n">
-        <v>4.465400000000001</v>
+        <v>4.4654</v>
       </c>
       <c r="L22" t="n">
         <v>14.3761</v>
@@ -2158,7 +2158,7 @@
         <v>-8.5848</v>
       </c>
       <c r="O22" t="n">
-        <v>-7.619200000000001</v>
+        <v>-7.6192</v>
       </c>
       <c r="P22" t="n">
         <v>2.9105</v>
@@ -2170,13 +2170,13 @@
         <v>15.5226</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9085000000000001</v>
+        <v>2.2432</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2302000000000005</v>
+        <v>-0.2302</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1385</v>
+        <v>2.4734</v>
       </c>
       <c r="V22" t="n">
         <v>9.1792</v>
